--- a/backend/src/templates/users-import.xlsx
+++ b/backend/src/templates/users-import.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF8E31C-988E-4D27-9AED-4A037F4CD045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179240F7-E813-41AD-BD1D-9534E1A19050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -480,7 +480,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
@@ -497,7 +497,7 @@
         <v>11</v>
       </c>
       <c r="D3" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>12</v>
@@ -514,7 +514,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>12</v>
